--- a/inspection_forms/044_electrical_injection_testing_form--inspection_forms.xlsx
+++ b/inspection_forms/044_electrical_injection_testing_form--inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Test Date and Time</t>
+          <t>Date and Time of Test</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -570,18 +570,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>form_page_2</t>
+          <t>form_page_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>equipment_id</t>
+          <t>Location of Test</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -593,118 +593,110 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_page_3</t>
+          <t>form_page_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Enter Location</t>
-        </is>
-      </c>
+          <t>Test Location</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_page_3</t>
+          <t>form_page_4_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>Test Parameters</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_page_4</t>
+          <t>form_page_5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Test Results</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_page_4</t>
+          <t>form_page_5_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>parameters</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_page_5</t>
+          <t>form_page_6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Results</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Enter Result</t>
-        </is>
-      </c>
+          <t>Inspection Date</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -716,168 +708,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_page_5</t>
+          <t>form_page_6_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>results</t>
+          <t>Test Type</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>form_page_6</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Additional Comments</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Additional Comments</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>form_page_6</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>additional_comments</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>form_page_7</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Inspection Date</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Enter Inspection Date</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>form_page_7</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>inspection_date</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>form_page_8</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Test Location</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Enter Test Location</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>form_page_8</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>test_location</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -892,12 +734,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -920,7 +762,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_page_4_choices</t>
+          <t>form_page_4_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -937,7 +779,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_page_4_choices</t>
+          <t>form_page_4_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -954,34 +796,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_page_4_choices</t>
+          <t>form_page_5_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_page_4_choices</t>
+          <t>form_page_5_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -993,97 +835,46 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>form_page_5_choices</t>
+          <t>form_page_6_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>electrical</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Electrical</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>form_page_5_choices</t>
+          <t>form_page_6_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>form_page_5_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>form_page_5_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>form_page_5_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>poor</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Poor</t>
+          <t>Mechanical</t>
         </is>
       </c>
     </row>
